--- a/ApplicationHealthCheckAfterPatch/Config/Applications.xlsx
+++ b/ApplicationHealthCheckAfterPatch/Config/Applications.xlsx
@@ -1,20 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\KARKA-SAAS-DEV\uipath-discussions\ApplicationHealthCheckAfterPatch\Config\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FF3E412A-3680-4F7E-8426-6E8CB0E8D0F4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{16E1F947-CDD0-49A6-BB08-B5EAB94ADFAB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{F6976F25-8881-4A74-BADF-7F3ECFBFE83F}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{F6976F25-8881-4A74-BADF-7F3ECFBFE83F}"/>
   </bookViews>
   <sheets>
     <sheet name="Applications" sheetId="1" r:id="rId1"/>
     <sheet name="TC_Outlook" sheetId="2" r:id="rId2"/>
+    <sheet name="TC_Excel" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Applications!$A$1:$I$1</definedName>
@@ -39,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="65" uniqueCount="47">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="106" uniqueCount="71">
   <si>
     <t>AppID</t>
   </si>
@@ -180,6 +181,78 @@
   </si>
   <si>
     <t>MasterReport_214023.html</t>
+  </si>
+  <si>
+    <t>APP003</t>
+  </si>
+  <si>
+    <t>Excel</t>
+  </si>
+  <si>
+    <t>C:\Program Files\Microsoft Office\Root\Office16\EXCEL.EXE</t>
+  </si>
+  <si>
+    <t>XL-S01</t>
+  </si>
+  <si>
+    <t>Launch Excel Application</t>
+  </si>
+  <si>
+    <t>CreateWorkbook</t>
+  </si>
+  <si>
+    <t>HealthCheck_{RunID}.xlsx</t>
+  </si>
+  <si>
+    <t>XL-S02</t>
+  </si>
+  <si>
+    <t>Write Content To Workbook</t>
+  </si>
+  <si>
+    <t>WriteContent</t>
+  </si>
+  <si>
+    <t>Post-patch health check run {RunID}</t>
+  </si>
+  <si>
+    <t>XL-S03</t>
+  </si>
+  <si>
+    <t>Open Existing File And Save As</t>
+  </si>
+  <si>
+    <t>OpenSaveAs</t>
+  </si>
+  <si>
+    <t>C:\HealthCheck\SampleFiles\ExistingWorkbook.xlsx|SavedAs_{RunID}.xlsx</t>
+  </si>
+  <si>
+    <t>XL-S04</t>
+  </si>
+  <si>
+    <t>Save File As Favorite</t>
+  </si>
+  <si>
+    <t>SaveAsFavorite</t>
+  </si>
+  <si>
+    <t>Favorite_{RunID}.xlsx</t>
+  </si>
+  <si>
+    <t>XL-S05</t>
+  </si>
+  <si>
+    <t>Create Single Sheet</t>
+  </si>
+  <si>
+    <t>CreateSheets</t>
+  </si>
+  <si>
+    <t>XL-S06</t>
+  </si>
+  <si>
+    <t>Create Multiple Sheets</t>
   </si>
 </sst>
 </file>
@@ -546,7 +619,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3BCA727B-EC70-4CD2-BD65-CA9321E07ECD}">
-  <dimension ref="A1:I3"/>
+  <dimension ref="A1:I4"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="13.21875" customWidth="1"/>
@@ -638,6 +711,32 @@
         <v>12</v>
       </c>
       <c r="I3" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>47</v>
+      </c>
+      <c r="B4" t="s">
+        <v>48</v>
+      </c>
+      <c r="C4" t="s">
+        <v>49</v>
+      </c>
+      <c r="E4" t="s">
+        <v>11</v>
+      </c>
+      <c r="F4">
+        <v>1</v>
+      </c>
+      <c r="G4">
+        <v>120</v>
+      </c>
+      <c r="H4" t="s">
+        <v>12</v>
+      </c>
+      <c r="I4" t="s">
         <v>44</v>
       </c>
     </row>
@@ -862,4 +961,175 @@
   <autoFilter ref="A1:N1" xr:uid="{1E6EB03E-86BD-4ACA-85FB-4025E04AC89B}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{29D9CCF8-685A-4DDB-AA30-63AB705A758B}">
+  <dimension ref="A1:G7"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetData>
+    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A1" t="s">
+        <v>17</v>
+      </c>
+      <c r="B1" t="s">
+        <v>18</v>
+      </c>
+      <c r="C1" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1" t="s">
+        <v>19</v>
+      </c>
+      <c r="E1" t="s">
+        <v>21</v>
+      </c>
+      <c r="F1" t="s">
+        <v>6</v>
+      </c>
+      <c r="G1" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>50</v>
+      </c>
+      <c r="B2" t="s">
+        <v>51</v>
+      </c>
+      <c r="C2" t="s">
+        <v>11</v>
+      </c>
+      <c r="D2" t="s">
+        <v>52</v>
+      </c>
+      <c r="E2" t="s">
+        <v>53</v>
+      </c>
+      <c r="F2">
+        <v>120</v>
+      </c>
+      <c r="G2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>54</v>
+      </c>
+      <c r="B3" t="s">
+        <v>55</v>
+      </c>
+      <c r="C3" t="s">
+        <v>11</v>
+      </c>
+      <c r="D3" t="s">
+        <v>56</v>
+      </c>
+      <c r="E3" t="s">
+        <v>57</v>
+      </c>
+      <c r="F3">
+        <v>60</v>
+      </c>
+      <c r="G3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>58</v>
+      </c>
+      <c r="B4" t="s">
+        <v>59</v>
+      </c>
+      <c r="C4" t="s">
+        <v>11</v>
+      </c>
+      <c r="D4" t="s">
+        <v>60</v>
+      </c>
+      <c r="E4" t="s">
+        <v>61</v>
+      </c>
+      <c r="F4">
+        <v>120</v>
+      </c>
+      <c r="G4">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>62</v>
+      </c>
+      <c r="B5" t="s">
+        <v>63</v>
+      </c>
+      <c r="C5" t="s">
+        <v>11</v>
+      </c>
+      <c r="D5" t="s">
+        <v>64</v>
+      </c>
+      <c r="E5" t="s">
+        <v>65</v>
+      </c>
+      <c r="F5">
+        <v>60</v>
+      </c>
+      <c r="G5">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
+        <v>66</v>
+      </c>
+      <c r="B6" t="s">
+        <v>67</v>
+      </c>
+      <c r="C6" t="s">
+        <v>11</v>
+      </c>
+      <c r="D6" t="s">
+        <v>68</v>
+      </c>
+      <c r="E6">
+        <v>1</v>
+      </c>
+      <c r="F6">
+        <v>60</v>
+      </c>
+      <c r="G6">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A7" t="s">
+        <v>69</v>
+      </c>
+      <c r="B7" t="s">
+        <v>70</v>
+      </c>
+      <c r="C7" t="s">
+        <v>11</v>
+      </c>
+      <c r="D7" t="s">
+        <v>68</v>
+      </c>
+      <c r="E7">
+        <v>3</v>
+      </c>
+      <c r="F7">
+        <v>60</v>
+      </c>
+      <c r="G7">
+        <v>6</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>